--- a/outputs/Wage_(non-qualified_labour,_agricultural)_percentile_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_agricultural)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="94">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>Minimal</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Alert</t>
@@ -853,7 +856,7 @@
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
         <v>79</v>
@@ -865,7 +868,7 @@
         <v>79</v>
       </c>
       <c r="J2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K2" t="s">
         <v>79</v>
@@ -883,7 +886,7 @@
         <v>79</v>
       </c>
       <c r="P2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q2" t="s">
         <v>79</v>
@@ -892,13 +895,13 @@
         <v>79</v>
       </c>
       <c r="S2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T2" t="s">
         <v>79</v>
       </c>
       <c r="U2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -913,88 +916,88 @@
         <v>79</v>
       </c>
       <c r="Z2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BA2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -1002,64 +1005,64 @@
         <v>54</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R3" t="s">
         <v>79</v>
       </c>
       <c r="S3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T3" t="s">
         <v>79</v>
       </c>
       <c r="U3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1068,94 +1071,94 @@
         <v>79</v>
       </c>
       <c r="X3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="s">
         <v>79</v>
       </c>
       <c r="AC3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1169,19 +1172,19 @@
         <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s">
         <v>79</v>
@@ -1208,10 +1211,10 @@
         <v>79</v>
       </c>
       <c r="Q4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S4" t="s">
         <v>79</v>
@@ -1229,25 +1232,25 @@
         <v>79</v>
       </c>
       <c r="X4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="s">
         <v>79</v>
       </c>
       <c r="AB4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC4" t="s">
         <v>79</v>
       </c>
       <c r="AD4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE4" t="s">
         <v>79</v>
@@ -1265,7 +1268,7 @@
         <v>79</v>
       </c>
       <c r="AJ4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK4" t="s">
         <v>79</v>
@@ -1274,16 +1277,16 @@
         <v>79</v>
       </c>
       <c r="AM4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AN4" t="s">
         <v>79</v>
       </c>
       <c r="AO4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AP4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ4" t="s">
         <v>79</v>
@@ -1304,19 +1307,19 @@
         <v>79</v>
       </c>
       <c r="AW4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AX4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AY4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AZ4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="BA4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1324,70 +1327,70 @@
         <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S5" t="s">
         <v>79</v>
       </c>
       <c r="T5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X5" t="s">
         <v>79</v>
@@ -1402,13 +1405,13 @@
         <v>79</v>
       </c>
       <c r="AB5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC5" t="s">
         <v>79</v>
       </c>
       <c r="AD5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1417,7 +1420,7 @@
         <v>79</v>
       </c>
       <c r="AG5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s">
         <v>79</v>
@@ -1426,7 +1429,7 @@
         <v>79</v>
       </c>
       <c r="AJ5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="s">
         <v>79</v>
@@ -1438,7 +1441,7 @@
         <v>79</v>
       </c>
       <c r="AN5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO5" t="s">
         <v>79</v>
@@ -1453,10 +1456,10 @@
         <v>79</v>
       </c>
       <c r="AS5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AU5" t="s">
         <v>79</v>
@@ -1465,19 +1468,19 @@
         <v>79</v>
       </c>
       <c r="AW5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX5" t="s">
         <v>79</v>
       </c>
       <c r="AY5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BA5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1485,55 +1488,55 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S6" t="s">
         <v>79</v>
@@ -1542,28 +1545,28 @@
         <v>79</v>
       </c>
       <c r="U6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W6" t="s">
         <v>79</v>
       </c>
       <c r="X6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC6" t="s">
         <v>79</v>
@@ -1578,13 +1581,13 @@
         <v>79</v>
       </c>
       <c r="AG6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="s">
         <v>79</v>
@@ -1596,34 +1599,34 @@
         <v>79</v>
       </c>
       <c r="AM6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AR6" t="s">
         <v>81</v>
       </c>
-      <c r="AR6" t="s">
-        <v>80</v>
-      </c>
       <c r="AS6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT6" t="s">
         <v>79</v>
       </c>
       <c r="AU6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW6" t="s">
         <v>79</v>
@@ -1632,13 +1635,13 @@
         <v>79</v>
       </c>
       <c r="AY6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AZ6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BA6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1646,121 +1649,121 @@
         <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO7" t="s">
         <v>79</v>
@@ -1769,37 +1772,37 @@
         <v>79</v>
       </c>
       <c r="AQ7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1807,55 +1810,55 @@
         <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S8" t="s">
         <v>79</v>
@@ -1867,7 +1870,7 @@
         <v>79</v>
       </c>
       <c r="V8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W8" t="s">
         <v>79</v>
@@ -1876,10 +1879,10 @@
         <v>79</v>
       </c>
       <c r="Y8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA8" t="s">
         <v>79</v>
@@ -1891,25 +1894,25 @@
         <v>79</v>
       </c>
       <c r="AD8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF8" t="s">
         <v>79</v>
       </c>
       <c r="AG8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH8" t="s">
         <v>79</v>
       </c>
       <c r="AI8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK8" t="s">
         <v>79</v>
@@ -1918,49 +1921,49 @@
         <v>79</v>
       </c>
       <c r="AM8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP8" t="s">
         <v>79</v>
       </c>
       <c r="AQ8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AR8" t="s">
         <v>79</v>
       </c>
       <c r="AS8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BA8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -1968,49 +1971,49 @@
         <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q9" t="s">
         <v>79</v>
@@ -2031,7 +2034,7 @@
         <v>79</v>
       </c>
       <c r="W9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X9" t="s">
         <v>79</v>
@@ -2043,7 +2046,7 @@
         <v>79</v>
       </c>
       <c r="AA9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB9" t="s">
         <v>79</v>
@@ -2073,10 +2076,10 @@
         <v>79</v>
       </c>
       <c r="AK9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="s">
         <v>79</v>
@@ -2085,43 +2088,43 @@
         <v>79</v>
       </c>
       <c r="AO9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AR9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AS9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AT9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AZ9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2129,55 +2132,55 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S10" t="s">
         <v>79</v>
@@ -2186,7 +2189,7 @@
         <v>79</v>
       </c>
       <c r="U10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -2195,13 +2198,13 @@
         <v>79</v>
       </c>
       <c r="X10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y10" t="s">
         <v>79</v>
       </c>
       <c r="Z10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA10" t="s">
         <v>79</v>
@@ -2210,79 +2213,79 @@
         <v>79</v>
       </c>
       <c r="AC10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK10" t="s">
         <v>79</v>
       </c>
       <c r="AL10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2290,121 +2293,121 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="s">
         <v>79</v>
@@ -2416,34 +2419,34 @@
         <v>79</v>
       </c>
       <c r="AR11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2451,142 +2454,142 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO12" t="s">
         <v>79</v>
       </c>
       <c r="AP12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT12" t="s">
         <v>79</v>
       </c>
       <c r="AU12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV12" t="s">
         <v>79</v>
@@ -2595,16 +2598,16 @@
         <v>79</v>
       </c>
       <c r="AX12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2612,19 +2615,19 @@
         <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s">
         <v>79</v>
@@ -2636,94 +2639,94 @@
         <v>79</v>
       </c>
       <c r="J13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="s">
         <v>79</v>
       </c>
       <c r="AM13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="s">
         <v>79</v>
@@ -2735,16 +2738,16 @@
         <v>79</v>
       </c>
       <c r="AQ13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AR13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AS13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AT13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU13" t="s">
         <v>79</v>
@@ -2753,19 +2756,19 @@
         <v>79</v>
       </c>
       <c r="AW13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="BA13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2773,55 +2776,55 @@
         <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S14" t="s">
         <v>79</v>
@@ -2842,7 +2845,7 @@
         <v>79</v>
       </c>
       <c r="Y14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z14" t="s">
         <v>79</v>
@@ -2857,28 +2860,28 @@
         <v>79</v>
       </c>
       <c r="AD14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL14" t="s">
         <v>79</v>
@@ -2896,7 +2899,7 @@
         <v>79</v>
       </c>
       <c r="AQ14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR14" t="s">
         <v>79</v>
@@ -2905,28 +2908,28 @@
         <v>79</v>
       </c>
       <c r="AT14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AW14" t="s">
         <v>79</v>
       </c>
       <c r="AX14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BA14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -2934,109 +2937,109 @@
         <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="s">
         <v>79</v>
@@ -3051,10 +3054,10 @@
         <v>79</v>
       </c>
       <c r="AO15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ15" t="s">
         <v>79</v>
@@ -3066,28 +3069,28 @@
         <v>79</v>
       </c>
       <c r="AT15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3095,115 +3098,115 @@
         <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="s">
         <v>79</v>
@@ -3224,7 +3227,7 @@
         <v>79</v>
       </c>
       <c r="AS16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT16" t="s">
         <v>79</v>
@@ -3242,13 +3245,13 @@
         <v>79</v>
       </c>
       <c r="AY16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3256,28 +3259,28 @@
         <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s">
         <v>79</v>
       </c>
       <c r="H17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J17" t="s">
         <v>79</v>
@@ -3286,13 +3289,13 @@
         <v>79</v>
       </c>
       <c r="L17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M17" t="s">
         <v>79</v>
       </c>
       <c r="N17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O17" t="s">
         <v>79</v>
@@ -3304,7 +3307,7 @@
         <v>79</v>
       </c>
       <c r="R17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S17" t="s">
         <v>79</v>
@@ -3340,7 +3343,7 @@
         <v>79</v>
       </c>
       <c r="AD17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE17" t="s">
         <v>79</v>
@@ -3355,61 +3358,61 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s">
         <v>81</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>80</v>
-      </c>
       <c r="AM17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP17" t="s">
         <v>79</v>
       </c>
       <c r="AQ17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AR17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AS17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AT17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AU17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AW17" t="s">
         <v>79</v>
       </c>
       <c r="AX17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AZ17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BA17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3420,7 +3423,7 @@
         <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>79</v>
@@ -3432,31 +3435,31 @@
         <v>79</v>
       </c>
       <c r="G18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s">
         <v>79</v>
       </c>
       <c r="I18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P18" t="s">
         <v>79</v>
@@ -3474,40 +3477,40 @@
         <v>79</v>
       </c>
       <c r="U18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
       </c>
       <c r="W18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y18" t="s">
         <v>79</v>
       </c>
       <c r="Z18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="s">
         <v>79</v>
       </c>
       <c r="AC18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE18" t="s">
         <v>79</v>
       </c>
       <c r="AF18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AG18" t="s">
         <v>79</v>
@@ -3522,55 +3525,55 @@
         <v>79</v>
       </c>
       <c r="AK18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AM18" t="s">
         <v>79</v>
       </c>
       <c r="AN18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AR18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AZ18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BA18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3587,7 +3590,7 @@
         <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
         <v>79</v>
@@ -3599,13 +3602,13 @@
         <v>79</v>
       </c>
       <c r="I19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J19" t="s">
         <v>79</v>
       </c>
       <c r="K19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L19" t="s">
         <v>79</v>
@@ -3623,7 +3626,7 @@
         <v>79</v>
       </c>
       <c r="Q19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R19" t="s">
         <v>79</v>
@@ -3635,10 +3638,10 @@
         <v>79</v>
       </c>
       <c r="U19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W19" t="s">
         <v>79</v>
@@ -3650,22 +3653,22 @@
         <v>79</v>
       </c>
       <c r="Z19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA19" t="s">
         <v>79</v>
       </c>
       <c r="AB19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC19" t="s">
         <v>79</v>
       </c>
       <c r="AD19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AE19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF19" t="s">
         <v>79</v>
@@ -3683,31 +3686,31 @@
         <v>79</v>
       </c>
       <c r="AK19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL19" t="s">
         <v>79</v>
       </c>
       <c r="AM19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO19" t="s">
         <v>79</v>
       </c>
       <c r="AP19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AR19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AS19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT19" t="s">
         <v>79</v>
@@ -3716,22 +3719,22 @@
         <v>79</v>
       </c>
       <c r="AV19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AW19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AY19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AZ19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BA19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3739,160 +3742,160 @@
         <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV20" t="s">
         <v>79</v>
       </c>
       <c r="AW20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3900,7 +3903,7 @@
         <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
         <v>79</v>
@@ -3909,67 +3912,67 @@
         <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
         <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
         <v>79</v>
       </c>
       <c r="I21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z21" t="s">
         <v>79</v>
@@ -3978,19 +3981,19 @@
         <v>79</v>
       </c>
       <c r="AB21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG21" t="s">
         <v>79</v>
@@ -4005,55 +4008,55 @@
         <v>79</v>
       </c>
       <c r="AK21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ21" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>79</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>79</v>
+      </c>
+      <c r="AU21" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX21" t="s">
         <v>81</v>
       </c>
-      <c r="AN21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AS21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AU21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AV21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AW21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX21" t="s">
-        <v>80</v>
-      </c>
       <c r="AY21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AZ21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BA21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4061,28 +4064,28 @@
         <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J22" t="s">
         <v>79</v>
@@ -4103,7 +4106,7 @@
         <v>79</v>
       </c>
       <c r="P22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q22" t="s">
         <v>79</v>
@@ -4124,7 +4127,7 @@
         <v>79</v>
       </c>
       <c r="W22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X22" t="s">
         <v>79</v>
@@ -4148,73 +4151,73 @@
         <v>79</v>
       </c>
       <c r="AE22" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF22" t="s">
         <v>81</v>
       </c>
-      <c r="AF22" t="s">
-        <v>80</v>
-      </c>
       <c r="AG22" t="s">
         <v>79</v>
       </c>
       <c r="AH22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s">
         <v>79</v>
       </c>
       <c r="AJ22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN22" t="s">
         <v>81</v>
       </c>
-      <c r="AM22" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN22" t="s">
-        <v>80</v>
-      </c>
       <c r="AO22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ22" t="s">
         <v>79</v>
       </c>
       <c r="AR22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AT22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AU22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AV22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AW22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AX22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AZ22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BA22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:53">
@@ -4222,25 +4225,25 @@
         <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s">
         <v>79</v>
       </c>
       <c r="H23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I23" t="s">
         <v>79</v>
@@ -4249,7 +4252,7 @@
         <v>79</v>
       </c>
       <c r="K23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L23" t="s">
         <v>79</v>
@@ -4261,7 +4264,7 @@
         <v>79</v>
       </c>
       <c r="O23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P23" t="s">
         <v>79</v>
@@ -4273,7 +4276,7 @@
         <v>79</v>
       </c>
       <c r="S23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T23" t="s">
         <v>79</v>
@@ -4294,10 +4297,10 @@
         <v>79</v>
       </c>
       <c r="Z23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB23" t="s">
         <v>79</v>
@@ -4315,7 +4318,7 @@
         <v>79</v>
       </c>
       <c r="AG23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s">
         <v>79</v>
@@ -4324,7 +4327,7 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK23" t="s">
         <v>79</v>
@@ -4342,14 +4345,14 @@
         <v>79</v>
       </c>
       <c r="AP23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR23" t="s">
         <v>81</v>
       </c>
-      <c r="AQ23" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>80</v>
-      </c>
       <c r="AS23" t="s">
         <v>79</v>
       </c>
@@ -4369,13 +4372,13 @@
         <v>79</v>
       </c>
       <c r="AY23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AZ23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="BA23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:53">
@@ -4383,19 +4386,19 @@
         <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
         <v>79</v>
@@ -4416,7 +4419,7 @@
         <v>79</v>
       </c>
       <c r="M24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N24" t="s">
         <v>79</v>
@@ -4434,13 +4437,13 @@
         <v>79</v>
       </c>
       <c r="S24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T24" t="s">
         <v>79</v>
       </c>
       <c r="U24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V24" t="s">
         <v>79</v>
@@ -4452,25 +4455,25 @@
         <v>79</v>
       </c>
       <c r="Y24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF24" t="s">
         <v>79</v>
@@ -4479,7 +4482,7 @@
         <v>79</v>
       </c>
       <c r="AH24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s">
         <v>79</v>
@@ -4497,7 +4500,7 @@
         <v>79</v>
       </c>
       <c r="AN24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AO24" t="s">
         <v>79</v>
@@ -4506,37 +4509,37 @@
         <v>79</v>
       </c>
       <c r="AQ24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AR24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AS24" t="s">
         <v>79</v>
       </c>
       <c r="AT24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AV24" t="s">
         <v>79</v>
       </c>
       <c r="AW24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BA24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:53">
@@ -4544,106 +4547,106 @@
         <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="s">
         <v>79</v>
@@ -4652,16 +4655,16 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP25" t="s">
         <v>79</v>
@@ -4679,25 +4682,25 @@
         <v>79</v>
       </c>
       <c r="AU25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AZ25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="BA25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:53">
@@ -4735,7 +4738,7 @@
         <v>79</v>
       </c>
       <c r="L26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M26" t="s">
         <v>79</v>
@@ -4753,7 +4756,7 @@
         <v>79</v>
       </c>
       <c r="R26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S26" t="s">
         <v>79</v>
@@ -4765,100 +4768,100 @@
         <v>79</v>
       </c>
       <c r="V26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AA26" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC26" t="s">
         <v>81</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AD26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP26" t="s">
         <v>81</v>
       </c>
-      <c r="AC26" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO26" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP26" t="s">
-        <v>80</v>
-      </c>
       <c r="AQ26" t="s">
         <v>79</v>
       </c>
       <c r="AR26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AS26" t="s">
         <v>79</v>
       </c>
       <c r="AT26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU26" t="s">
         <v>79</v>
       </c>
       <c r="AV26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AY26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AZ26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="BA26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:53">
@@ -4893,13 +4896,13 @@
         <v>79</v>
       </c>
       <c r="K27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L27" t="s">
         <v>79</v>
       </c>
       <c r="M27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N27" t="s">
         <v>79</v>
@@ -4908,32 +4911,32 @@
         <v>79</v>
       </c>
       <c r="P27" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>79</v>
+      </c>
+      <c r="R27" t="s">
+        <v>80</v>
+      </c>
+      <c r="S27" t="s">
+        <v>79</v>
+      </c>
+      <c r="T27" t="s">
+        <v>79</v>
+      </c>
+      <c r="U27" t="s">
+        <v>79</v>
+      </c>
+      <c r="V27" t="s">
+        <v>79</v>
+      </c>
+      <c r="W27" t="s">
+        <v>80</v>
+      </c>
+      <c r="X27" t="s">
         <v>81</v>
       </c>
-      <c r="Q27" t="s">
-        <v>79</v>
-      </c>
-      <c r="R27" t="s">
-        <v>79</v>
-      </c>
-      <c r="S27" t="s">
-        <v>79</v>
-      </c>
-      <c r="T27" t="s">
-        <v>79</v>
-      </c>
-      <c r="U27" t="s">
-        <v>79</v>
-      </c>
-      <c r="V27" t="s">
-        <v>79</v>
-      </c>
-      <c r="W27" t="s">
-        <v>79</v>
-      </c>
-      <c r="X27" t="s">
-        <v>80</v>
-      </c>
       <c r="Y27" t="s">
         <v>79</v>
       </c>
@@ -4950,7 +4953,7 @@
         <v>79</v>
       </c>
       <c r="AD27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE27" t="s">
         <v>79</v>
@@ -4974,52 +4977,52 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AM27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ27" t="s">
         <v>81</v>
       </c>
-      <c r="AN27" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO27" t="s">
+      <c r="AR27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU27" t="s">
         <v>81</v>
       </c>
-      <c r="AP27" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ27" t="s">
-        <v>80</v>
-      </c>
-      <c r="AR27" t="s">
+      <c r="AV27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW27" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX27" t="s">
         <v>81</v>
       </c>
-      <c r="AS27" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT27" t="s">
-        <v>81</v>
-      </c>
-      <c r="AU27" t="s">
-        <v>80</v>
-      </c>
-      <c r="AV27" t="s">
-        <v>79</v>
-      </c>
-      <c r="AW27" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX27" t="s">
-        <v>80</v>
-      </c>
       <c r="AY27" t="s">
+        <v>87</v>
+      </c>
+      <c r="AZ27" t="s">
+        <v>87</v>
+      </c>
+      <c r="BA27" t="s">
         <v>86</v>
-      </c>
-      <c r="AZ27" t="s">
-        <v>86</v>
-      </c>
-      <c r="BA27" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Wage_(non-qualified_labour,_agricultural)_percentile_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_agricultural)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="82">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -259,43 +259,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>22%</t>
-  </si>
-  <si>
-    <t>31%</t>
-  </si>
-  <si>
-    <t>18%</t>
   </si>
 </sst>
 </file>
@@ -865,7 +829,7 @@
         <v>79</v>
       </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J2" t="s">
         <v>80</v>
@@ -886,16 +850,16 @@
         <v>79</v>
       </c>
       <c r="P2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q2" t="s">
         <v>79</v>
       </c>
       <c r="R2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="T2" t="s">
         <v>79</v>
@@ -904,7 +868,7 @@
         <v>80</v>
       </c>
       <c r="V2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W2" t="s">
         <v>79</v>
@@ -991,13 +955,13 @@
         <v>80</v>
       </c>
       <c r="AY2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="BA2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -1053,22 +1017,22 @@
         <v>80</v>
       </c>
       <c r="R3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S3" t="s">
         <v>80</v>
       </c>
       <c r="T3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U3" t="s">
         <v>80</v>
       </c>
       <c r="V3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X3" t="s">
         <v>80</v>
@@ -1083,7 +1047,7 @@
         <v>80</v>
       </c>
       <c r="AB3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC3" t="s">
         <v>80</v>
@@ -1152,13 +1116,13 @@
         <v>80</v>
       </c>
       <c r="AY3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1277,13 +1241,13 @@
         <v>79</v>
       </c>
       <c r="AM4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AN4" t="s">
         <v>79</v>
       </c>
       <c r="AO4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AP4" t="s">
         <v>80</v>
@@ -1307,19 +1271,19 @@
         <v>79</v>
       </c>
       <c r="AW4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AX4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AY4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AZ4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="BA4" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1447,7 +1411,7 @@
         <v>79</v>
       </c>
       <c r="AP5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ5" t="s">
         <v>79</v>
@@ -1459,7 +1423,7 @@
         <v>80</v>
       </c>
       <c r="AT5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AU5" t="s">
         <v>79</v>
@@ -1474,13 +1438,13 @@
         <v>79</v>
       </c>
       <c r="AY5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="BA5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1551,7 +1515,7 @@
         <v>80</v>
       </c>
       <c r="W6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X6" t="s">
         <v>80</v>
@@ -1569,10 +1533,10 @@
         <v>80</v>
       </c>
       <c r="AC6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE6" t="s">
         <v>79</v>
@@ -1590,7 +1554,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK6" t="s">
         <v>79</v>
@@ -1611,16 +1575,16 @@
         <v>80</v>
       </c>
       <c r="AQ6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AR6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AS6" t="s">
         <v>80</v>
       </c>
       <c r="AT6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU6" t="s">
         <v>80</v>
@@ -1635,13 +1599,13 @@
         <v>79</v>
       </c>
       <c r="AY6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AZ6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="BA6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1766,10 +1730,10 @@
         <v>80</v>
       </c>
       <c r="AO7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ7" t="s">
         <v>80</v>
@@ -1796,13 +1760,13 @@
         <v>80</v>
       </c>
       <c r="AY7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1867,13 +1831,13 @@
         <v>79</v>
       </c>
       <c r="U8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V8" t="s">
         <v>80</v>
       </c>
       <c r="W8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X8" t="s">
         <v>79</v>
@@ -1885,13 +1849,13 @@
         <v>80</v>
       </c>
       <c r="AA8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD8" t="s">
         <v>80</v>
@@ -1906,19 +1870,19 @@
         <v>80</v>
       </c>
       <c r="AH8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI8" t="s">
         <v>80</v>
       </c>
       <c r="AJ8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AK8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM8" t="s">
         <v>80</v>
@@ -1930,10 +1894,10 @@
         <v>80</v>
       </c>
       <c r="AP8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AR8" t="s">
         <v>79</v>
@@ -1957,13 +1921,13 @@
         <v>80</v>
       </c>
       <c r="AY8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ8" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="BA8" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -2016,10 +1980,10 @@
         <v>80</v>
       </c>
       <c r="Q9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S9" t="s">
         <v>79</v>
@@ -2031,19 +1995,19 @@
         <v>79</v>
       </c>
       <c r="V9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W9" t="s">
         <v>80</v>
       </c>
       <c r="X9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="s">
         <v>80</v>
@@ -2052,10 +2016,10 @@
         <v>79</v>
       </c>
       <c r="AC9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE9" t="s">
         <v>79</v>
@@ -2067,13 +2031,13 @@
         <v>79</v>
       </c>
       <c r="AH9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK9" t="s">
         <v>80</v>
@@ -2082,7 +2046,7 @@
         <v>80</v>
       </c>
       <c r="AM9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s">
         <v>79</v>
@@ -2094,13 +2058,13 @@
         <v>80</v>
       </c>
       <c r="AQ9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AR9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AS9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AT9" t="s">
         <v>80</v>
@@ -2118,13 +2082,13 @@
         <v>80</v>
       </c>
       <c r="AY9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AZ9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2183,19 +2147,19 @@
         <v>80</v>
       </c>
       <c r="S10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U10" t="s">
         <v>80</v>
       </c>
       <c r="V10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X10" t="s">
         <v>80</v>
@@ -2207,10 +2171,10 @@
         <v>80</v>
       </c>
       <c r="AA10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC10" t="s">
         <v>80</v>
@@ -2279,13 +2243,13 @@
         <v>80</v>
       </c>
       <c r="AY10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2410,13 +2374,13 @@
         <v>80</v>
       </c>
       <c r="AO11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR11" t="s">
         <v>80</v>
@@ -2440,13 +2404,13 @@
         <v>80</v>
       </c>
       <c r="AY11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2571,7 +2535,7 @@
         <v>80</v>
       </c>
       <c r="AO12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP12" t="s">
         <v>80</v>
@@ -2586,28 +2550,28 @@
         <v>80</v>
       </c>
       <c r="AT12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU12" t="s">
         <v>80</v>
       </c>
       <c r="AV12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX12" t="s">
         <v>80</v>
       </c>
       <c r="AY12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2723,37 +2687,37 @@
         <v>80</v>
       </c>
       <c r="AL13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="s">
         <v>80</v>
       </c>
       <c r="AN13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AR13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AS13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AT13" t="s">
         <v>80</v>
       </c>
       <c r="AU13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW13" t="s">
         <v>80</v>
@@ -2762,13 +2726,13 @@
         <v>80</v>
       </c>
       <c r="AY13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="BA13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2827,7 +2791,7 @@
         <v>80</v>
       </c>
       <c r="S14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T14" t="s">
         <v>79</v>
@@ -2836,10 +2800,10 @@
         <v>79</v>
       </c>
       <c r="V14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X14" t="s">
         <v>79</v>
@@ -2896,7 +2860,7 @@
         <v>79</v>
       </c>
       <c r="AP14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ14" t="s">
         <v>80</v>
@@ -2914,22 +2878,22 @@
         <v>80</v>
       </c>
       <c r="AV14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AW14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX14" t="s">
         <v>80</v>
       </c>
       <c r="AY14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="BA14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -3042,16 +3006,16 @@
         <v>80</v>
       </c>
       <c r="AK15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO15" t="s">
         <v>80</v>
@@ -3060,13 +3024,13 @@
         <v>80</v>
       </c>
       <c r="AQ15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT15" t="s">
         <v>80</v>
@@ -3084,13 +3048,13 @@
         <v>80</v>
       </c>
       <c r="AY15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3209,49 +3173,49 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS16" t="s">
         <v>80</v>
       </c>
       <c r="AT16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AV16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AX16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AY16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3358,46 +3322,46 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AJ17" t="s">
         <v>79</v>
       </c>
       <c r="AK17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AM17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AN17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AO17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AP17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AR17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AS17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AT17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AU17" t="s">
         <v>80</v>
       </c>
       <c r="AV17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AW17" t="s">
         <v>79</v>
@@ -3406,13 +3370,13 @@
         <v>80</v>
       </c>
       <c r="AY17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AZ17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="BA17" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3489,7 +3453,7 @@
         <v>80</v>
       </c>
       <c r="Y18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z18" t="s">
         <v>80</v>
@@ -3510,28 +3474,28 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AG18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s">
         <v>79</v>
       </c>
       <c r="AI18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK18" t="s">
         <v>80</v>
       </c>
       <c r="AL18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AM18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="s">
         <v>80</v>
@@ -3543,7 +3507,7 @@
         <v>80</v>
       </c>
       <c r="AQ18" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AR18" t="s">
         <v>80</v>
@@ -3567,13 +3531,13 @@
         <v>80</v>
       </c>
       <c r="AY18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AZ18" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="BA18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3665,7 +3629,7 @@
         <v>79</v>
       </c>
       <c r="AD19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AE19" t="s">
         <v>80</v>
@@ -3674,7 +3638,7 @@
         <v>79</v>
       </c>
       <c r="AG19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s">
         <v>79</v>
@@ -3686,7 +3650,7 @@
         <v>79</v>
       </c>
       <c r="AK19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AL19" t="s">
         <v>79</v>
@@ -3695,7 +3659,7 @@
         <v>80</v>
       </c>
       <c r="AN19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AO19" t="s">
         <v>79</v>
@@ -3704,10 +3668,10 @@
         <v>80</v>
       </c>
       <c r="AQ19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AR19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AS19" t="s">
         <v>80</v>
@@ -3719,22 +3683,22 @@
         <v>79</v>
       </c>
       <c r="AV19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AW19" t="s">
         <v>80</v>
       </c>
       <c r="AX19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AY19" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AZ19" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="BA19" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3880,7 +3844,7 @@
         <v>80</v>
       </c>
       <c r="AV20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AW20" t="s">
         <v>80</v>
@@ -3889,13 +3853,13 @@
         <v>80</v>
       </c>
       <c r="AY20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3909,13 +3873,13 @@
         <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
         <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s">
         <v>80</v>
@@ -4014,19 +3978,19 @@
         <v>80</v>
       </c>
       <c r="AM21" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AN21" t="s">
         <v>80</v>
       </c>
       <c r="AO21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="s">
         <v>80</v>
       </c>
       <c r="AQ21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR21" t="s">
         <v>79</v>
@@ -4047,16 +4011,16 @@
         <v>80</v>
       </c>
       <c r="AX21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AY21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AZ21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="BA21" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4151,40 +4115,40 @@
         <v>79</v>
       </c>
       <c r="AE22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AF22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AG22" t="s">
         <v>79</v>
       </c>
       <c r="AH22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s">
         <v>79</v>
       </c>
       <c r="AJ22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AK22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AL22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AM22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AN22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AO22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AP22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AQ22" t="s">
         <v>79</v>
@@ -4193,31 +4157,31 @@
         <v>80</v>
       </c>
       <c r="AS22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AT22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AU22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AV22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AW22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AX22" t="s">
         <v>80</v>
       </c>
       <c r="AY22" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AZ22" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="BA22" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:53">
@@ -4276,7 +4240,7 @@
         <v>79</v>
       </c>
       <c r="S23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="T23" t="s">
         <v>79</v>
@@ -4300,7 +4264,7 @@
         <v>80</v>
       </c>
       <c r="AA23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AB23" t="s">
         <v>79</v>
@@ -4345,13 +4309,13 @@
         <v>79</v>
       </c>
       <c r="AP23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AQ23" t="s">
         <v>80</v>
       </c>
       <c r="AR23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AS23" t="s">
         <v>79</v>
@@ -4372,13 +4336,13 @@
         <v>79</v>
       </c>
       <c r="AY23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AZ23" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="BA23" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:53">
@@ -4482,7 +4446,7 @@
         <v>79</v>
       </c>
       <c r="AH24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s">
         <v>79</v>
@@ -4491,7 +4455,7 @@
         <v>79</v>
       </c>
       <c r="AK24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL24" t="s">
         <v>79</v>
@@ -4500,7 +4464,7 @@
         <v>79</v>
       </c>
       <c r="AN24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AO24" t="s">
         <v>79</v>
@@ -4509,10 +4473,10 @@
         <v>79</v>
       </c>
       <c r="AQ24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AR24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AS24" t="s">
         <v>79</v>
@@ -4521,7 +4485,7 @@
         <v>80</v>
       </c>
       <c r="AU24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AV24" t="s">
         <v>79</v>
@@ -4533,13 +4497,13 @@
         <v>80</v>
       </c>
       <c r="AY24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ24" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="BA24" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:53">
@@ -4649,10 +4613,10 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="s">
         <v>80</v>
@@ -4667,19 +4631,19 @@
         <v>80</v>
       </c>
       <c r="AP25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU25" t="s">
         <v>80</v>
@@ -4694,13 +4658,13 @@
         <v>80</v>
       </c>
       <c r="AY25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AZ25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BA25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:53">
@@ -4768,28 +4732,28 @@
         <v>79</v>
       </c>
       <c r="V26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="W26" t="s">
         <v>80</v>
       </c>
       <c r="X26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Y26" t="s">
         <v>80</v>
       </c>
       <c r="Z26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AA26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AB26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AC26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AD26" t="s">
         <v>80</v>
@@ -4828,13 +4792,13 @@
         <v>79</v>
       </c>
       <c r="AP26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AQ26" t="s">
         <v>79</v>
       </c>
       <c r="AR26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AS26" t="s">
         <v>79</v>
@@ -4852,16 +4816,16 @@
         <v>80</v>
       </c>
       <c r="AX26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AY26" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AZ26" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="BA26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:53">
@@ -4881,7 +4845,7 @@
         <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s">
         <v>79</v>
@@ -4911,7 +4875,7 @@
         <v>79</v>
       </c>
       <c r="P27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Q27" t="s">
         <v>79</v>
@@ -4935,7 +4899,7 @@
         <v>80</v>
       </c>
       <c r="X27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Y27" t="s">
         <v>79</v>
@@ -4977,34 +4941,34 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AM27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AN27" t="s">
         <v>80</v>
       </c>
       <c r="AO27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AP27" t="s">
         <v>80</v>
       </c>
       <c r="AQ27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AR27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AS27" t="s">
         <v>80</v>
       </c>
       <c r="AT27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AU27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AV27" t="s">
         <v>80</v>
@@ -5013,16 +4977,16 @@
         <v>79</v>
       </c>
       <c r="AX27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AY27" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AZ27" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="BA27" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Wage_(non-qualified_labour,_agricultural)_percentile_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_agricultural)_percentile_classification_matrix.xlsx
@@ -253,7 +253,7 @@
     <t>Yambio</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
